--- a/data/trans_bre/P1412-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1412-Clase-trans_bre.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-46,53%</t>
+          <t>-46,07%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,22</t>
+          <t>-2,51; -0,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,31</t>
+          <t>-1,76; 0,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 71,91</t>
+          <t>-87,78; 68,44</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-72,1%</t>
+          <t>-75,11%</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,0</t>
+          <t>-1,33; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,15</t>
+          <t>-1,4; 0,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-64,07%</t>
+          <t>-78,5%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; -0,17</t>
+          <t>-2,4; -0,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; -0,16</t>
+          <t>-1,69; -0,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,81</t>
+          <t>-2,2; -0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 535,12</t>
+          <t>-100,0; 41,04</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-59,61%</t>
+          <t>-43,54%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,28</t>
+          <t>-1,75; -0,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; -0,03</t>
+          <t>-1,47; -0,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,0</t>
+          <t>-1,17; 0,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,58</t>
+          <t>-100,0; -1,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,74</t>
+          <t>-100,0; 26,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 4,28</t>
+          <t>-80,65; 45,7</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-36,95%</t>
+          <t>-7,93%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,79</t>
+          <t>-0,64; 1,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,56</t>
+          <t>-1,63; 0,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,28</t>
+          <t>-0,75; 0,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 595,03</t>
+          <t>-51,51; 577,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,3; 117,48</t>
+          <t>-84,4; 107,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 93,52</t>
+          <t>-68,46; 252,87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,75</t>
+          <t>0,48; 1,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,85</t>
+          <t>0,51; 1,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,2</t>
+          <t>0,33; 1,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-44,58%</t>
+          <t>-39,75%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,38</t>
+          <t>-0,37; 0,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,19</t>
+          <t>-0,64; 0,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; -0,08</t>
+          <t>-0,79; -0,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,57; 84,2</t>
+          <t>-41,3; 106,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 40,05</t>
+          <t>-63,03; 39,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-65,43; -9,49</t>
+          <t>-63,21; -6,78</t>
         </is>
       </c>
     </row>
